--- a/public/assets/templates/grad-engineering-portfolio-checklist.xlsx
+++ b/public/assets/templates/grad-engineering-portfolio-checklist.xlsx
@@ -398,13 +398,13 @@
     <t>檢查一下是不是這段時間都在寫內容、沒有回頭處理缺口。內容寫得再多，缺的那幾項還是缺。</t>
   </si>
   <si>
-    <t>搭配文章：理工研究所備審怎麼寫，把團隊專題變成個人貢獻　https://tbd-web.vercel.app/pages/resources/engineering-graduate-cv.html?utm_source=tbd-web&amp;utm_medium=template&amp;utm_campaign=grad-engineering-portfolio-checklist</t>
+    <t>搭配文章：理工研究所備審怎麼寫，把團隊專題變成個人貢獻　https://tbd-edu.com/pages/resources/engineering-graduate-cv.html?utm_source=tbd-web&amp;utm_medium=template&amp;utm_campaign=grad-engineering-portfolio-checklist</t>
   </si>
   <si>
     <t>上一階段是研究計畫書、下一階段是口試。備審裡列出的技術能力，要能延伸到計畫書的方法段落。</t>
   </si>
   <si>
-    <t>TBD Studio ｜ 研究所申請陪跑計畫　https://tbd-web.vercel.app/pages/resources/tools.html</t>
+    <t>TBD Studio ｜ 研究所申請陪跑計畫　https://tbd-edu.com/pages/resources/tools.html</t>
   </si>
   <si>
     <t>唯一要寫字的地方，而且只寫關鍵字。這頁是後面打勾的依據，完整文字版在另外幾份表。</t>
